--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -2392,7 +2392,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GAPHT121</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -2496,7 +2496,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>GAMAT101</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">

--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -2,28 +2,44 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="480" yWindow="4545" windowWidth="21705" windowHeight="8580" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet name="s1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="s2" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="s3" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="s4" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="s5" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="s6" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="s7" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="s8" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="2">
+  <fonts count="4">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="Calibri"/>
+      <b val="1"/>
+      <sz val="11"/>
     </font>
     <font>
       <b val="1"/>
@@ -37,12 +53,42 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="4">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -55,14 +101,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -429,42 +481,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="1" t="inlineStr">
+      <c r="A1" s="3" t="inlineStr">
         <is>
           <t>week_day</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
+      <c r="B1" s="3" t="inlineStr">
         <is>
           <t>slot_1</t>
         </is>
       </c>
-      <c r="C1" s="1" t="inlineStr">
+      <c r="C1" s="3" t="inlineStr">
         <is>
           <t>slot_2</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="D1" s="3" t="inlineStr">
         <is>
           <t>slot_3</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="E1" s="3" t="inlineStr">
         <is>
           <t>slot_4</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="F1" s="3" t="inlineStr">
         <is>
           <t>slot_5</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="G1" s="3" t="inlineStr">
         <is>
           <t>slot_6</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="H1" s="3" t="inlineStr">
         <is>
           <t>slot_x</t>
         </is>
@@ -483,17 +535,17 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAPHT121,(L)</t>
+          <t>GAMAT101(T),ROSA,ELVIZ,EZRI</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>GAPHT121(P)</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,ZVL,ZADIE</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -520,27 +572,27 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>GXEST104(T),ZVL,ELVIZ</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>GMEST103(P)</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>ROSA,ZVL</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
           <t>ROSA,CE,GAMAT101,(L)</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ROSA,CE,GAPHT121,(L)</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>FREE</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>FREE</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>FREE</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -562,12 +614,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ZVL,CE,GMEST103,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>UCHUT128(T),ZADIE</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -604,7 +656,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -624,17 +676,17 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>UCEST105(P)</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>NIVI,ELVIZ</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>ZADIE,CE,UCHUT128,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
     </row>
@@ -666,21 +718,1883 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>GXESL106(P)</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ELVIZ,NIVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>ZADIE,CE,UCHUT128,(L)</t>
+          <t>FREE</t>
         </is>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:H6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>week_day</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>slot_1</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>slot_2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>slot_3</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>slot_4</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>slot_5</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>slot_6</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>slot_x</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>monday</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>tuesday</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>wednesday</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>thursday</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>friday</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>FREE</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/timeTable_CE.xlsx
+++ b/timeTable_CE.xlsx
@@ -23,18 +23,13 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="4">
+  <fonts count="3">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
       <color theme="1"/>
       <sz val="11"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <name val="Calibri"/>
-      <b val="1"/>
-      <sz val="11"/>
     </font>
     <font>
       <name val="Calibri"/>
@@ -53,27 +48,12 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="4">
+  <borders count="3">
     <border>
       <left/>
       <right/>
       <top/>
       <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -101,15 +81,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -481,42 +458,42 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
-      <c r="A1" s="3" t="inlineStr">
+      <c r="A1" s="2" t="inlineStr">
         <is>
           <t>week_day</t>
         </is>
       </c>
-      <c r="B1" s="3" t="inlineStr">
+      <c r="B1" s="2" t="inlineStr">
         <is>
           <t>slot_1</t>
         </is>
       </c>
-      <c r="C1" s="3" t="inlineStr">
+      <c r="C1" s="2" t="inlineStr">
         <is>
           <t>slot_2</t>
         </is>
       </c>
-      <c r="D1" s="3" t="inlineStr">
+      <c r="D1" s="2" t="inlineStr">
         <is>
           <t>slot_3</t>
         </is>
       </c>
-      <c r="E1" s="3" t="inlineStr">
+      <c r="E1" s="2" t="inlineStr">
         <is>
           <t>slot_4</t>
         </is>
       </c>
-      <c r="F1" s="3" t="inlineStr">
+      <c r="F1" s="2" t="inlineStr">
         <is>
           <t>slot_5</t>
         </is>
       </c>
-      <c r="G1" s="3" t="inlineStr">
+      <c r="G1" s="2" t="inlineStr">
         <is>
           <t>slot_6</t>
         </is>
       </c>
-      <c r="H1" s="3" t="inlineStr">
+      <c r="H1" s="2" t="inlineStr">
         <is>
           <t>slot_x</t>
         </is>
@@ -530,12 +507,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>NIVI,CE,GAPHT121,(L)</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>GAMAT101(T),ROSA,ELVIZ,EZRI</t>
+          <t>EZRI,CE,GMEST103,(L)</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
@@ -545,7 +522,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>ROSA,ZVL,ZADIE</t>
+          <t>ROSA,ZVL,ZADIE,NIVI</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -572,12 +549,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>EZRI,CE,GMEST103,(L)</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>GXEST104(T),ZVL,ELVIZ</t>
+          <t>GXEST104(T),ELVIZ,ZVL</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -587,12 +564,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ROSA,ZVL</t>
+          <t>ZVL,ROSA,EZRI,EZER</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ROSA,CE,GAMAT101,(L)</t>
+          <t>ZADIE,CE,UCEST105,(L)</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -614,27 +591,27 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ANJANA,CE,GXEST104,(L)</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>UCHUT128(T),ZADIE</t>
+          <t>GAMAT101(T),ROSA,CHINO,ELVIZ</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZADIE,CE,UCEST105,(L)</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZVL,CE,UCHUT128,(L)</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZADIE,CE,UCEST105,(L)</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -656,22 +633,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>UCHUT128(T),ZVL</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ZVL,CE,UCHUT128,(L)</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -681,7 +658,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>NIVI,ELVIZ</t>
+          <t>EZER,EZRI,ROSA,ZVL</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -698,22 +675,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>NIVI,CE,GAPHT121,(L)</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ROSA,CE,GAMAT101,(L)</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>NIVI,CE,GAPHT121,(L)</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>FREE</t>
+          <t>ANJANA,CE,GXEST104,(L)</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -723,7 +700,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>ELVIZ,NIVI</t>
+          <t>ZADIE,EZER,EZRI,NIVI</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
